--- a/CYP2C19_Allele_def_rs_excluidos.xlsx
+++ b/CYP2C19_Allele_def_rs_excluidos.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23010" windowHeight="9015" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Salida_R" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="76">
   <si>
     <t>rsID</t>
   </si>
@@ -208,18 +208,12 @@
     <t>rs/*alelo</t>
   </si>
   <si>
-    <t xml:space="preserve">UCSC </t>
-  </si>
-  <si>
     <t>https://genome.ucsc.edu/cgi-bin/hgTracks?db=hg38&amp;lastVirtModeType=default&amp;lastVirtModeExtraState=&amp;virtModeType=default&amp;virtMode=0&amp;nonVirtPosition=&amp;position=chr10%3A94762756%2D94762956&amp;hgsid=3905166663_KBL3qZi4UyAi0gcJo5M43LQObARb</t>
   </si>
   <si>
     <t>GenomAD</t>
   </si>
   <si>
-    <t>0.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">Error </t>
   </si>
   <si>
@@ -242,13 +236,25 @@
   </si>
   <si>
     <t>https://gnomad.broadinstitute.org/variant/10-94775423-A-C?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs1564657013</t>
+  </si>
+  <si>
+    <t>UCSC, dbSNP</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs1564656981</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs1564660997#hgvs_tab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +270,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -271,12 +285,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -296,6 +304,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -306,23 +320,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -924,13 +941,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="13" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -980,12 +997,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1020,7 +1037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1030,8 +1047,8 @@
       <c r="M4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N4" t="s">
-        <v>65</v>
+      <c r="N4">
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>60</v>
@@ -1040,7 +1057,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1050,8 +1067,8 @@
       <c r="M5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N5" t="s">
-        <v>65</v>
+      <c r="N5">
+        <v>0</v>
       </c>
       <c r="O5" t="s">
         <v>60</v>
@@ -1060,24 +1077,27 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="7" t="s">
         <v>3</v>
       </c>
       <c r="O6" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="P6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1091,30 +1111,33 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="O8" t="s">
-        <v>62</v>
-      </c>
-      <c r="P8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -1128,30 +1151,33 @@
         <v>8.3900000000000006E-5</v>
       </c>
       <c r="O9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="7" t="s">
         <v>5</v>
       </c>
       <c r="O10" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="P10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -1161,17 +1187,17 @@
       <c r="M11" t="s">
         <v>6</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="5">
         <v>8.4740000000000003E-7</v>
       </c>
       <c r="O11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -1185,35 +1211,35 @@
         <v>6.1870000000000002E-5</v>
       </c>
       <c r="O12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
       <c r="L13" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
       <c r="L14" t="s">
         <v>52</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -1227,15 +1253,15 @@
         <v>8.051E-5</v>
       </c>
       <c r="O15" t="s">
+        <v>63</v>
+      </c>
+      <c r="P15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
         <v>64</v>
-      </c>
-      <c r="P15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="M16" t="s">
-        <v>66</v>
       </c>
       <c r="N16">
         <f>SUM(N4:N15)*100</f>
@@ -1243,6 +1269,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="P6" r:id="rId1"/>
+    <hyperlink ref="P8" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>